--- a/VerveStacks_CHN_grids_kan60/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHN_grids_kan60/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan60\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F219A7BC-5601-44D0-AD3B-5DB0CA7A4916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C3D071-7A7A-4CBD-A084-3C7D5570A6ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="21600" windowHeight="12772" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="controller" sheetId="5" r:id="rId1"/>

--- a/VerveStacks_CHN_grids_kan60/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHN_grids_kan60/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan60\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C3D071-7A7A-4CBD-A084-3C7D5570A6ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADDC826-8561-496C-808D-8CFD8EDAA260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN_grids_kan60/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHN_grids_kan60/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan60\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADDC826-8561-496C-808D-8CFD8EDAA260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F9BFA0-BABC-4168-8692-8476B8A902A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN_grids_kan60/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHN_grids_kan60/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan60\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F9BFA0-BABC-4168-8692-8476B8A902A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36BB8DE3-48FC-4C00-B471-1DD9B96079AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHN_grids_kan60/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHN_grids_kan60/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan60\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36BB8DE3-48FC-4C00-B471-1DD9B96079AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD7DD759-2900-4E2C-B4FB-220A245C0A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12773" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="controller" sheetId="5" r:id="rId1"/>

--- a/VerveStacks_CHN_grids_kan60/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHN_grids_kan60/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan60\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD7DD759-2900-4E2C-B4FB-220A245C0A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4F807DC-43CC-4FC7-AAF3-040FF0BC7C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12773" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
